--- a/data/nzd0130/nzd0130.xlsx
+++ b/data/nzd0130/nzd0130.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K630"/>
+  <dimension ref="A1:K631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25008,6 +25008,45 @@
       <c r="K630" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>419.82</v>
+      </c>
+      <c r="C631" t="n">
+        <v>409.55</v>
+      </c>
+      <c r="D631" t="n">
+        <v>395.47</v>
+      </c>
+      <c r="E631" t="n">
+        <v>387.93</v>
+      </c>
+      <c r="F631" t="n">
+        <v>394.09</v>
+      </c>
+      <c r="G631" t="n">
+        <v>387.03</v>
+      </c>
+      <c r="H631" t="n">
+        <v>377.58</v>
+      </c>
+      <c r="I631" t="n">
+        <v>379.82</v>
+      </c>
+      <c r="J631" t="n">
+        <v>419.02</v>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25022,7 +25061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B638"/>
+  <dimension ref="A1:B639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31405,6 +31444,16 @@
       </c>
       <c r="B638" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -31573,28 +31622,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2317163021758503</v>
+        <v>-0.235650892527629</v>
       </c>
       <c r="J2" t="n">
+        <v>630</v>
+      </c>
+      <c r="K2" t="n">
         <v>629</v>
       </c>
-      <c r="K2" t="n">
-        <v>628</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02509129417184908</v>
+        <v>0.02596392952675963</v>
       </c>
       <c r="M2" t="n">
-        <v>8.008625188375527</v>
+        <v>8.017315655081488</v>
       </c>
       <c r="N2" t="n">
-        <v>111.8290362437581</v>
+        <v>111.8871599966477</v>
       </c>
       <c r="O2" t="n">
-        <v>10.57492488123476</v>
+        <v>10.57767271173804</v>
       </c>
       <c r="P2" t="n">
-        <v>438.1195004597226</v>
+        <v>438.160600358383</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31655,28 +31704,28 @@
         <v>0.0261</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1726425128165775</v>
+        <v>-0.1737941774884533</v>
       </c>
       <c r="J3" t="n">
+        <v>630</v>
+      </c>
+      <c r="K3" t="n">
         <v>629</v>
       </c>
-      <c r="K3" t="n">
-        <v>628</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.05799388188781684</v>
+        <v>0.05887615970890581</v>
       </c>
       <c r="M3" t="n">
-        <v>4.057474988487816</v>
+        <v>4.056873182115779</v>
       </c>
       <c r="N3" t="n">
-        <v>25.95180432687278</v>
+        <v>25.93075723848361</v>
       </c>
       <c r="O3" t="n">
-        <v>5.094291346877677</v>
+        <v>5.092225175547878</v>
       </c>
       <c r="P3" t="n">
-        <v>417.6579937821689</v>
+        <v>417.6700238277577</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31737,28 +31786,28 @@
         <v>0.0367</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1348354041815385</v>
+        <v>-0.1357569838801545</v>
       </c>
       <c r="J4" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="K4" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05997115433377109</v>
+        <v>0.0608964342122239</v>
       </c>
       <c r="M4" t="n">
-        <v>3.093802819256035</v>
+        <v>3.093569116433198</v>
       </c>
       <c r="N4" t="n">
-        <v>15.25520576985623</v>
+        <v>15.24390855142058</v>
       </c>
       <c r="O4" t="n">
-        <v>3.905791311611032</v>
+        <v>3.904344829983716</v>
       </c>
       <c r="P4" t="n">
-        <v>401.8733513741814</v>
+        <v>401.8829818782804</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31819,28 +31868,28 @@
         <v>0.0459</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04886118399370896</v>
+        <v>-0.05008974251950668</v>
       </c>
       <c r="J5" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="K5" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004862999011132962</v>
+        <v>0.005122802287406025</v>
       </c>
       <c r="M5" t="n">
-        <v>4.006348427125456</v>
+        <v>4.007353824270068</v>
       </c>
       <c r="N5" t="n">
-        <v>26.15279329263077</v>
+        <v>26.13423716488422</v>
       </c>
       <c r="O5" t="n">
-        <v>5.113980181094836</v>
+        <v>5.112165604211607</v>
       </c>
       <c r="P5" t="n">
-        <v>393.0277955043522</v>
+        <v>393.0406339359456</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -31901,28 +31950,28 @@
         <v>0.0475</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01039438165860562</v>
+        <v>-0.01080942415923449</v>
       </c>
       <c r="J6" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="K6" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002468920711745648</v>
+        <v>0.0002679081906690195</v>
       </c>
       <c r="M6" t="n">
-        <v>3.854380797009869</v>
+        <v>3.850288116138764</v>
       </c>
       <c r="N6" t="n">
-        <v>23.4204024297151</v>
+        <v>23.38584714526507</v>
       </c>
       <c r="O6" t="n">
-        <v>4.839463031134249</v>
+        <v>4.83589155640044</v>
       </c>
       <c r="P6" t="n">
-        <v>395.6468658210756</v>
+        <v>395.6512030135176</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -31983,28 +32032,28 @@
         <v>0.0573</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03699381878565382</v>
+        <v>0.03473466824011107</v>
       </c>
       <c r="J7" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="K7" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003079093528151389</v>
+        <v>0.002716167647617174</v>
       </c>
       <c r="M7" t="n">
-        <v>3.86236398732042</v>
+        <v>3.864730399533448</v>
       </c>
       <c r="N7" t="n">
-        <v>23.71961128556918</v>
+        <v>23.75958572220412</v>
       </c>
       <c r="O7" t="n">
-        <v>4.870278358119705</v>
+        <v>4.874380547536694</v>
       </c>
       <c r="P7" t="n">
-        <v>393.0702105347556</v>
+        <v>393.09381864876</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32065,28 +32114,28 @@
         <v>0.0639</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.07315244731914114</v>
+        <v>-0.0760661169057625</v>
       </c>
       <c r="J8" t="n">
+        <v>630</v>
+      </c>
+      <c r="K8" t="n">
         <v>629</v>
       </c>
-      <c r="K8" t="n">
-        <v>628</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01115845434887752</v>
+        <v>0.01203548856983705</v>
       </c>
       <c r="M8" t="n">
-        <v>3.970901599306839</v>
+        <v>3.973981623547474</v>
       </c>
       <c r="N8" t="n">
-        <v>25.42325939352645</v>
+        <v>25.51220987507073</v>
       </c>
       <c r="O8" t="n">
-        <v>5.042148291504966</v>
+        <v>5.050961282277933</v>
       </c>
       <c r="P8" t="n">
-        <v>388.5459047937723</v>
+        <v>388.5763366457418</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32147,28 +32196,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1471307715201493</v>
+        <v>-0.1498943840970897</v>
       </c>
       <c r="J9" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="K9" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03728951417909632</v>
+        <v>0.03863545326643836</v>
       </c>
       <c r="M9" t="n">
-        <v>4.36699783458415</v>
+        <v>4.370167638876542</v>
       </c>
       <c r="N9" t="n">
-        <v>29.91764583157199</v>
+        <v>29.98631932959152</v>
       </c>
       <c r="O9" t="n">
-        <v>5.469702535931181</v>
+        <v>5.475976564010434</v>
       </c>
       <c r="P9" t="n">
-        <v>392.2566307181697</v>
+        <v>392.2855104583486</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32229,28 +32278,28 @@
         <v>0.0202</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1769547116236389</v>
+        <v>0.1735389971932692</v>
       </c>
       <c r="J10" t="n">
+        <v>630</v>
+      </c>
+      <c r="K10" t="n">
         <v>629</v>
       </c>
-      <c r="K10" t="n">
-        <v>628</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.03475027721110591</v>
+        <v>0.03345662874962796</v>
       </c>
       <c r="M10" t="n">
-        <v>5.303066116162186</v>
+        <v>5.30934886944517</v>
       </c>
       <c r="N10" t="n">
-        <v>46.62364150932979</v>
+        <v>46.72731111699883</v>
       </c>
       <c r="O10" t="n">
-        <v>6.828150665394678</v>
+        <v>6.835737788783215</v>
       </c>
       <c r="P10" t="n">
-        <v>424.9700879834138</v>
+        <v>425.0057678139399</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -32292,7 +32341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K630"/>
+  <dimension ref="A1:K631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68189,6 +68238,63 @@
         </is>
       </c>
     </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>-36.51852715413534,174.72178880454229</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>-36.519182848076035,174.72139295743617</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>-36.51982177054429,174.72095879209695</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>-36.520487389763154,174.72062908049875</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>-36.52118344835886,174.7204692413592</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>-36.52186059955279,174.7202355977052</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>-36.52255963865447,174.72005247125384</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>-36.52326087862302,174.7200313988293</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>-36.52389241842283,174.72059496764334</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0130/nzd0130.xlsx
+++ b/data/nzd0130/nzd0130.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K631"/>
+  <dimension ref="A1:K633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25047,6 +25047,84 @@
       <c r="K631" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>418.54</v>
+      </c>
+      <c r="C632" t="n">
+        <v>410.8</v>
+      </c>
+      <c r="D632" t="n">
+        <v>396.17</v>
+      </c>
+      <c r="E632" t="n">
+        <v>387.96</v>
+      </c>
+      <c r="F632" t="n">
+        <v>394.69</v>
+      </c>
+      <c r="G632" t="n">
+        <v>386.95</v>
+      </c>
+      <c r="H632" t="n">
+        <v>376.6</v>
+      </c>
+      <c r="I632" t="n">
+        <v>380.42</v>
+      </c>
+      <c r="J632" t="n">
+        <v>419.49</v>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>421.06</v>
+      </c>
+      <c r="C633" t="n">
+        <v>413.1</v>
+      </c>
+      <c r="D633" t="n">
+        <v>397.7</v>
+      </c>
+      <c r="E633" t="n">
+        <v>388.42</v>
+      </c>
+      <c r="F633" t="n">
+        <v>395.36</v>
+      </c>
+      <c r="G633" t="n">
+        <v>387.95</v>
+      </c>
+      <c r="H633" t="n">
+        <v>377.9</v>
+      </c>
+      <c r="I633" t="n">
+        <v>381.21</v>
+      </c>
+      <c r="J633" t="n">
+        <v>421.06</v>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25061,7 +25139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B639"/>
+  <dimension ref="A1:B641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31454,6 +31532,26 @@
       </c>
       <c r="B639" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -31622,28 +31720,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.235650892527629</v>
+        <v>-0.2434261151096241</v>
       </c>
       <c r="J2" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K2" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02596392952675963</v>
+        <v>0.02773254925742175</v>
       </c>
       <c r="M2" t="n">
-        <v>8.017315655081488</v>
+        <v>8.034202906845007</v>
       </c>
       <c r="N2" t="n">
-        <v>111.8871599966477</v>
+        <v>112.0020210429761</v>
       </c>
       <c r="O2" t="n">
-        <v>10.57767271173804</v>
+        <v>10.58310072913303</v>
       </c>
       <c r="P2" t="n">
-        <v>438.160600358383</v>
+        <v>438.2418904391014</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31704,28 +31802,28 @@
         <v>0.0261</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1737941774884533</v>
+        <v>-0.1745286974733845</v>
       </c>
       <c r="J3" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K3" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05887615970890581</v>
+        <v>0.05971869655833961</v>
       </c>
       <c r="M3" t="n">
-        <v>4.056873182115779</v>
+        <v>4.047769645389175</v>
       </c>
       <c r="N3" t="n">
-        <v>25.93075723848361</v>
+        <v>25.85691721673471</v>
       </c>
       <c r="O3" t="n">
-        <v>5.092225175547878</v>
+        <v>5.084969736068712</v>
       </c>
       <c r="P3" t="n">
-        <v>417.6700238277577</v>
+        <v>417.6777028340632</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31786,28 +31884,28 @@
         <v>0.0367</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1357569838801545</v>
+        <v>-0.1366395574264941</v>
       </c>
       <c r="J4" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K4" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0608964342122239</v>
+        <v>0.06201786073460225</v>
       </c>
       <c r="M4" t="n">
-        <v>3.093569116433198</v>
+        <v>3.08823594863834</v>
       </c>
       <c r="N4" t="n">
-        <v>15.24390855142058</v>
+        <v>15.2034839663921</v>
       </c>
       <c r="O4" t="n">
-        <v>3.904344829983716</v>
+        <v>3.899164521585631</v>
       </c>
       <c r="P4" t="n">
-        <v>401.8829818782804</v>
+        <v>401.8922126478666</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31868,28 +31966,28 @@
         <v>0.0459</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05008974251950668</v>
+        <v>-0.05234867825763728</v>
       </c>
       <c r="J5" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K5" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005122802287406025</v>
+        <v>0.00562324482440868</v>
       </c>
       <c r="M5" t="n">
-        <v>4.007353824270068</v>
+        <v>4.008234032133478</v>
       </c>
       <c r="N5" t="n">
-        <v>26.13423716488422</v>
+        <v>26.09082744887019</v>
       </c>
       <c r="O5" t="n">
-        <v>5.112165604211607</v>
+        <v>5.107918112976185</v>
       </c>
       <c r="P5" t="n">
-        <v>393.0406339359456</v>
+        <v>393.064260660404</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -31950,28 +32048,28 @@
         <v>0.0475</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01080942415923449</v>
+        <v>-0.01102832247041105</v>
       </c>
       <c r="J6" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K6" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002679081906690195</v>
+        <v>0.0002808143453012502</v>
       </c>
       <c r="M6" t="n">
-        <v>3.850288116138764</v>
+        <v>3.839166601260127</v>
       </c>
       <c r="N6" t="n">
-        <v>23.38584714526507</v>
+        <v>23.31256659088362</v>
       </c>
       <c r="O6" t="n">
-        <v>4.83589155640044</v>
+        <v>4.82830887484258</v>
       </c>
       <c r="P6" t="n">
-        <v>395.6512030135176</v>
+        <v>395.6534923957322</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -32032,28 +32130,28 @@
         <v>0.0573</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03473466824011107</v>
+        <v>0.03054166633254354</v>
       </c>
       <c r="J7" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K7" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002716167647617174</v>
+        <v>0.002103978380848415</v>
       </c>
       <c r="M7" t="n">
-        <v>3.864730399533448</v>
+        <v>3.868284602784635</v>
       </c>
       <c r="N7" t="n">
-        <v>23.75958572220412</v>
+        <v>23.82000862320856</v>
       </c>
       <c r="O7" t="n">
-        <v>4.874380547536694</v>
+        <v>4.880574620186496</v>
       </c>
       <c r="P7" t="n">
-        <v>393.09381864876</v>
+        <v>393.1376741815291</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32114,28 +32212,28 @@
         <v>0.0639</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0760661169057625</v>
+        <v>-0.08202698984173062</v>
       </c>
       <c r="J8" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K8" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01203548856983705</v>
+        <v>0.01391696145616161</v>
       </c>
       <c r="M8" t="n">
-        <v>3.973981623547474</v>
+        <v>3.980690579138443</v>
       </c>
       <c r="N8" t="n">
-        <v>25.51220987507073</v>
+        <v>25.70567767042224</v>
       </c>
       <c r="O8" t="n">
-        <v>5.050961282277933</v>
+        <v>5.070076692755469</v>
       </c>
       <c r="P8" t="n">
-        <v>388.5763366457418</v>
+        <v>388.6386501711176</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32196,28 +32294,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1498943840970897</v>
+        <v>-0.1547077227562</v>
       </c>
       <c r="J9" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K9" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03863545326643836</v>
+        <v>0.04109460273903087</v>
       </c>
       <c r="M9" t="n">
-        <v>4.370167638876542</v>
+        <v>4.374015719918575</v>
       </c>
       <c r="N9" t="n">
-        <v>29.98631932959152</v>
+        <v>30.06958286073791</v>
       </c>
       <c r="O9" t="n">
-        <v>5.475976564010434</v>
+        <v>5.483573913127998</v>
       </c>
       <c r="P9" t="n">
-        <v>392.2855104583486</v>
+        <v>392.3358543014041</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32278,28 +32376,28 @@
         <v>0.0202</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1735389971932692</v>
+        <v>0.1676017276375879</v>
       </c>
       <c r="J10" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K10" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03345662874962796</v>
+        <v>0.03131182500777907</v>
       </c>
       <c r="M10" t="n">
-        <v>5.30934886944517</v>
+        <v>5.31840439748085</v>
       </c>
       <c r="N10" t="n">
-        <v>46.72731111699883</v>
+        <v>46.85200365384078</v>
       </c>
       <c r="O10" t="n">
-        <v>6.835737788783215</v>
+        <v>6.84485234711756</v>
       </c>
       <c r="P10" t="n">
-        <v>425.0057678139399</v>
+        <v>425.067842135144</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -32341,7 +32439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K631"/>
+  <dimension ref="A1:K633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68295,6 +68393,120 @@
         </is>
       </c>
     </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>-36.51852360420993,174.72177520599064</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>-36.51918631482944,174.72140623737445</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>-36.51982358824427,174.72096627675114</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>-36.520487459169836,174.72062940425255</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>-36.521184560964834,174.72047579765515</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>-36.52186051207912,174.72023471101062</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>-36.52255913161388,174.72004154635974</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>-36.523260544110045,174.72003808581806</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>-36.52389172928694,174.72060014595658</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>-36.51853059312409,174.7218019781403</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>-36.51919269365175,174.72143067246384</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>-36.519827561215415,174.72098263606784</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>-36.52048852340561,174.72063436847765</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>-36.52118580337441,174.72048311885248</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>-36.52186160549945,174.7202457946931</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>-36.522559804218524,174.7200560385662</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>-36.52326010366738,174.72004689035313</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>-36.523889427278164,174.72061744372562</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0130/nzd0130.xlsx
+++ b/data/nzd0130/nzd0130.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K633"/>
+  <dimension ref="A1:K635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25123,6 +25123,84 @@
         <v>421.06</v>
       </c>
       <c r="K633" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>421.04</v>
+      </c>
+      <c r="C634" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="D634" t="n">
+        <v>396.96</v>
+      </c>
+      <c r="E634" t="n">
+        <v>389.29</v>
+      </c>
+      <c r="F634" t="n">
+        <v>395.63</v>
+      </c>
+      <c r="G634" t="n">
+        <v>387.34</v>
+      </c>
+      <c r="H634" t="n">
+        <v>377.19</v>
+      </c>
+      <c r="I634" t="n">
+        <v>381.54</v>
+      </c>
+      <c r="J634" t="n">
+        <v>423.29</v>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>421.93</v>
+      </c>
+      <c r="C635" t="n">
+        <v>413.34</v>
+      </c>
+      <c r="D635" t="n">
+        <v>397.74</v>
+      </c>
+      <c r="E635" t="n">
+        <v>389.71</v>
+      </c>
+      <c r="F635" t="n">
+        <v>395.93</v>
+      </c>
+      <c r="G635" t="n">
+        <v>387.66</v>
+      </c>
+      <c r="H635" t="n">
+        <v>378.31</v>
+      </c>
+      <c r="I635" t="n">
+        <v>381.94</v>
+      </c>
+      <c r="J635" t="n">
+        <v>422.31</v>
+      </c>
+      <c r="K635" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25139,7 +25217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B641"/>
+  <dimension ref="A1:B643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31552,6 +31630,26 @@
       </c>
       <c r="B641" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -31720,28 +31818,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2434261151096241</v>
+        <v>-0.250012713008536</v>
       </c>
       <c r="J2" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K2" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02773254925742175</v>
+        <v>0.02932293938577168</v>
       </c>
       <c r="M2" t="n">
-        <v>8.034202906845007</v>
+        <v>8.044586049845414</v>
       </c>
       <c r="N2" t="n">
-        <v>112.0020210429761</v>
+        <v>111.9830906205974</v>
       </c>
       <c r="O2" t="n">
-        <v>10.58310072913303</v>
+        <v>10.58220632101819</v>
       </c>
       <c r="P2" t="n">
-        <v>438.2418904391014</v>
+        <v>438.3109852721919</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31802,28 +31900,28 @@
         <v>0.0261</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1745286974733845</v>
+        <v>-0.1745966221286376</v>
       </c>
       <c r="J3" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K3" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05971869655833961</v>
+        <v>0.06015589864459314</v>
       </c>
       <c r="M3" t="n">
-        <v>4.047769645389175</v>
+        <v>4.036158363535699</v>
       </c>
       <c r="N3" t="n">
-        <v>25.85691721673471</v>
+        <v>25.77568855964274</v>
       </c>
       <c r="O3" t="n">
-        <v>5.084969736068712</v>
+        <v>5.076976320571402</v>
       </c>
       <c r="P3" t="n">
-        <v>417.6777028340632</v>
+        <v>417.6784142207317</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31884,28 +31982,28 @@
         <v>0.0367</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1366395574264941</v>
+        <v>-0.1372389549685593</v>
       </c>
       <c r="J4" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K4" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06201786073460225</v>
+        <v>0.06292818922982568</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08823594863834</v>
+        <v>3.081489783800227</v>
       </c>
       <c r="N4" t="n">
-        <v>15.2034839663921</v>
+        <v>15.15878100428508</v>
       </c>
       <c r="O4" t="n">
-        <v>3.899164521585631</v>
+        <v>3.89342792462954</v>
       </c>
       <c r="P4" t="n">
-        <v>401.8922126478666</v>
+        <v>401.8985018012315</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31966,28 +32064,28 @@
         <v>0.0459</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05234867825763728</v>
+        <v>-0.05373905929870328</v>
       </c>
       <c r="J5" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K5" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00562324482440868</v>
+        <v>0.00596209235895051</v>
       </c>
       <c r="M5" t="n">
-        <v>4.008234032133478</v>
+        <v>4.003858919857434</v>
       </c>
       <c r="N5" t="n">
-        <v>26.09082744887019</v>
+        <v>26.02352973995584</v>
       </c>
       <c r="O5" t="n">
-        <v>5.107918112976185</v>
+        <v>5.101326272642815</v>
       </c>
       <c r="P5" t="n">
-        <v>393.064260660404</v>
+        <v>393.0788514118761</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -32048,28 +32146,28 @@
         <v>0.0475</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01102832247041105</v>
+        <v>-0.01076145509107751</v>
       </c>
       <c r="J6" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K6" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002808143453012502</v>
+        <v>0.0002692634279770623</v>
       </c>
       <c r="M6" t="n">
-        <v>3.839166601260127</v>
+        <v>3.828388460256018</v>
       </c>
       <c r="N6" t="n">
-        <v>23.31256659088362</v>
+        <v>23.2396458249254</v>
       </c>
       <c r="O6" t="n">
-        <v>4.82830887484258</v>
+        <v>4.820751582992573</v>
       </c>
       <c r="P6" t="n">
-        <v>395.6534923957322</v>
+        <v>395.6506912626265</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -32130,28 +32228,28 @@
         <v>0.0573</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03054166633254354</v>
+        <v>0.02643513299503909</v>
       </c>
       <c r="J7" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K7" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002103978380848415</v>
+        <v>0.001579506889045734</v>
       </c>
       <c r="M7" t="n">
-        <v>3.868284602784635</v>
+        <v>3.871686634104499</v>
       </c>
       <c r="N7" t="n">
-        <v>23.82000862320856</v>
+        <v>23.8746380973545</v>
       </c>
       <c r="O7" t="n">
-        <v>4.880574620186496</v>
+        <v>4.886168038182324</v>
       </c>
       <c r="P7" t="n">
-        <v>393.1376741815291</v>
+        <v>393.1807698753199</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32212,28 +32310,28 @@
         <v>0.0639</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08202698984173062</v>
+        <v>-0.08758684241434636</v>
       </c>
       <c r="J8" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K8" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01391696145616161</v>
+        <v>0.01580094048907366</v>
       </c>
       <c r="M8" t="n">
-        <v>3.980690579138443</v>
+        <v>3.986111151886627</v>
       </c>
       <c r="N8" t="n">
-        <v>25.70567767042224</v>
+        <v>25.86365978981307</v>
       </c>
       <c r="O8" t="n">
-        <v>5.070076692755469</v>
+        <v>5.085632683335779</v>
       </c>
       <c r="P8" t="n">
-        <v>388.6386501711176</v>
+        <v>388.6969665212674</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32294,28 +32392,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1547077227562</v>
+        <v>-0.1588624669585489</v>
       </c>
       <c r="J9" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K9" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04109460273903087</v>
+        <v>0.04334160616414884</v>
       </c>
       <c r="M9" t="n">
-        <v>4.374015719918575</v>
+        <v>4.375640293807478</v>
       </c>
       <c r="N9" t="n">
-        <v>30.06958286073791</v>
+        <v>30.10761301760588</v>
       </c>
       <c r="O9" t="n">
-        <v>5.483573913127998</v>
+        <v>5.487040460722509</v>
       </c>
       <c r="P9" t="n">
-        <v>392.3358543014041</v>
+        <v>392.3794558048556</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32376,28 +32474,28 @@
         <v>0.0202</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1676017276375879</v>
+        <v>0.1633406964612486</v>
       </c>
       <c r="J10" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K10" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03131182500777907</v>
+        <v>0.02990236218938669</v>
       </c>
       <c r="M10" t="n">
-        <v>5.31840439748085</v>
+        <v>5.320218129980571</v>
       </c>
       <c r="N10" t="n">
-        <v>46.85200365384078</v>
+        <v>46.84462380023845</v>
       </c>
       <c r="O10" t="n">
-        <v>6.84485234711756</v>
+        <v>6.844313245332833</v>
       </c>
       <c r="P10" t="n">
-        <v>425.067842135144</v>
+        <v>425.1125437653728</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -32439,7 +32537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K633"/>
+  <dimension ref="A1:K635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68507,6 +68605,120 @@
         </is>
       </c>
     </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>-36.51853053765655,174.72180176566292</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>-36.51919130695169,174.72142536048756</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>-36.51982563964796,174.72097472371837</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>-36.52049053619877,174.72064375733848</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>-36.521186304046786,174.7204860691858</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>-36.52186093851317,174.72023903364675</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>-36.52255943687313,174.72004812359188</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>-36.523259919684826,174.72005056819685</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>-36.52388615754169,174.72064201316633</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>-36.51853300596208,174.7218112209073</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>-36.5191933592677,174.7214332222125</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>-36.51982766508391,174.7209830637624</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>-36.52049150789178,174.72064828989215</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>-36.521186860349346,174.72048934733397</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>-36.521861288407656,174.72024258042515</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>-36.522560016347306,174.7200606091852</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>-36.523259696675495,174.72005502618924</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>-36.52388759446685,174.72063121583392</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0130/nzd0130.xlsx
+++ b/data/nzd0130/nzd0130.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K635"/>
+  <dimension ref="A1:K636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25201,6 +25201,45 @@
         <v>422.31</v>
       </c>
       <c r="K635" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>429.74</v>
+      </c>
+      <c r="C636" t="n">
+        <v>411.7</v>
+      </c>
+      <c r="D636" t="n">
+        <v>396.87</v>
+      </c>
+      <c r="E636" t="n">
+        <v>389.24</v>
+      </c>
+      <c r="F636" t="n">
+        <v>393.65</v>
+      </c>
+      <c r="G636" t="n">
+        <v>388.2</v>
+      </c>
+      <c r="H636" t="n">
+        <v>379.52</v>
+      </c>
+      <c r="I636" t="n">
+        <v>381.68</v>
+      </c>
+      <c r="J636" t="n">
+        <v>424.42</v>
+      </c>
+      <c r="K636" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25217,7 +25256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B643"/>
+  <dimension ref="A1:B644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31650,6 +31689,16 @@
       </c>
       <c r="B643" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>-0.21</v>
       </c>
     </row>
   </sheetData>
@@ -31818,34 +31867,30 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.250012713008536</v>
+        <v>-0.2506373032691282</v>
       </c>
       <c r="J2" t="n">
+        <v>635</v>
+      </c>
+      <c r="K2" t="n">
         <v>634</v>
       </c>
-      <c r="K2" t="n">
-        <v>633</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02932293938577168</v>
+        <v>0.02956482476578948</v>
       </c>
       <c r="M2" t="n">
-        <v>8.044586049845414</v>
+        <v>8.035299515484454</v>
       </c>
       <c r="N2" t="n">
-        <v>111.9830906205974</v>
+        <v>111.8124471816835</v>
       </c>
       <c r="O2" t="n">
-        <v>10.58220632101819</v>
+        <v>10.57414049375567</v>
       </c>
       <c r="P2" t="n">
-        <v>438.3109852721919</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>438.317565218799</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.7173287557262 -36.51736274902051, 174.7271201976483 -36.51991877745389)</t>
@@ -31900,34 +31945,30 @@
         <v>0.0261</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1745966221286376</v>
+        <v>-0.1750300583643584</v>
       </c>
       <c r="J3" t="n">
+        <v>635</v>
+      </c>
+      <c r="K3" t="n">
         <v>634</v>
       </c>
-      <c r="K3" t="n">
-        <v>633</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.06015589864459314</v>
+        <v>0.0606311192584752</v>
       </c>
       <c r="M3" t="n">
-        <v>4.036158363535699</v>
+        <v>4.031979102768275</v>
       </c>
       <c r="N3" t="n">
-        <v>25.77568855964274</v>
+        <v>25.73791560141779</v>
       </c>
       <c r="O3" t="n">
-        <v>5.076976320571402</v>
+        <v>5.073254931640808</v>
       </c>
       <c r="P3" t="n">
-        <v>417.6784142207317</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>417.6829803938992</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.71704197939616 -36.518046919558934, 174.72683347274824 -36.52060295369539)</t>
@@ -31982,34 +32023,30 @@
         <v>0.0367</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1372389549685593</v>
+        <v>-0.1376864173684013</v>
       </c>
       <c r="J4" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K4" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06292818922982568</v>
+        <v>0.06351078984663916</v>
       </c>
       <c r="M4" t="n">
-        <v>3.081489783800227</v>
+        <v>3.078848129135118</v>
       </c>
       <c r="N4" t="n">
-        <v>15.15878100428508</v>
+        <v>15.13797531581615</v>
       </c>
       <c r="O4" t="n">
-        <v>3.89342792462954</v>
+        <v>3.890755108692418</v>
       </c>
       <c r="P4" t="n">
-        <v>401.8985018012315</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>401.9032175337979</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.71673033650504 -36.51879477126918, 174.72658503542593 -36.5211879844441)</t>
@@ -32064,34 +32101,30 @@
         <v>0.0459</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05373905929870328</v>
+        <v>-0.05451208644646736</v>
       </c>
       <c r="J5" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K5" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00596209235895051</v>
+        <v>0.006153195389456356</v>
       </c>
       <c r="M5" t="n">
-        <v>4.003858919857434</v>
+        <v>4.00210552772494</v>
       </c>
       <c r="N5" t="n">
-        <v>26.02352973995584</v>
+        <v>25.99169959828325</v>
       </c>
       <c r="O5" t="n">
-        <v>5.101326272642815</v>
+        <v>5.098205527269694</v>
       </c>
       <c r="P5" t="n">
-        <v>393.0788514118761</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>393.0869982177236</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.71644266565514 -36.519589817022535, 174.72638923686702 -36.52172209806239)</t>
@@ -32146,34 +32179,30 @@
         <v>0.0475</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01076145509107751</v>
+        <v>-0.01130913143874299</v>
       </c>
       <c r="J6" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K6" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002692634279770623</v>
+        <v>0.0002983515032369821</v>
       </c>
       <c r="M6" t="n">
-        <v>3.828388460256018</v>
+        <v>3.825022380166969</v>
       </c>
       <c r="N6" t="n">
-        <v>23.2396458249254</v>
+        <v>23.20764168000905</v>
       </c>
       <c r="O6" t="n">
-        <v>4.820751582992573</v>
+        <v>4.817431024935288</v>
       </c>
       <c r="P6" t="n">
-        <v>395.6506912626265</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>395.6564631334909</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (174.71616299448442 -36.52045259120365, 174.7262346547888 -36.5221616886152)</t>
@@ -32228,34 +32257,30 @@
         <v>0.0573</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02643513299503909</v>
+        <v>0.02461946033906559</v>
       </c>
       <c r="J7" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K7" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001579506889045734</v>
+        <v>0.001372207580981999</v>
       </c>
       <c r="M7" t="n">
-        <v>3.871686634104499</v>
+        <v>3.872516768384673</v>
       </c>
       <c r="N7" t="n">
-        <v>23.8746380973545</v>
+        <v>23.8875286753402</v>
       </c>
       <c r="O7" t="n">
-        <v>4.886168038182324</v>
+        <v>4.887486948866482</v>
       </c>
       <c r="P7" t="n">
-        <v>393.1807698753199</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>393.1999049505285</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (174.71594590040732 -36.52143733509959, 174.72616222689933 -36.52244511746233)</t>
@@ -32310,34 +32335,30 @@
         <v>0.0639</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08758684241434636</v>
+        <v>-0.08977982815941841</v>
       </c>
       <c r="J8" t="n">
+        <v>635</v>
+      </c>
+      <c r="K8" t="n">
         <v>634</v>
       </c>
-      <c r="K8" t="n">
-        <v>633</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01580094048907366</v>
+        <v>0.01659980554171081</v>
       </c>
       <c r="M8" t="n">
-        <v>3.986111151886627</v>
+        <v>3.986868384495617</v>
       </c>
       <c r="N8" t="n">
-        <v>25.86365978981307</v>
+        <v>25.89665963456459</v>
       </c>
       <c r="O8" t="n">
-        <v>5.085632683335779</v>
+        <v>5.088876067911714</v>
       </c>
       <c r="P8" t="n">
-        <v>388.6969665212674</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>388.7200664076109</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (174.71584327320357 -36.52236420875845, 174.72611889268813 -36.522841034343415)</t>
@@ -32392,34 +32413,30 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1588624669585489</v>
+        <v>-0.1609392567950386</v>
       </c>
       <c r="J9" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K9" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04334160616414884</v>
+        <v>0.04448823923833745</v>
       </c>
       <c r="M9" t="n">
-        <v>4.375640293807478</v>
+        <v>4.376453596771886</v>
       </c>
       <c r="N9" t="n">
-        <v>30.10761301760588</v>
+        <v>30.12625387435684</v>
       </c>
       <c r="O9" t="n">
-        <v>5.487040460722509</v>
+        <v>5.488738823660389</v>
       </c>
       <c r="P9" t="n">
-        <v>392.3794558048556</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>392.4013427510421</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>LINESTRING (174.71579829745437 -36.52347256151193, 174.72607122836018 -36.52295858572465)</t>
@@ -32474,34 +32491,30 @@
         <v>0.0202</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1633406964612486</v>
+        <v>0.1617363622499969</v>
       </c>
       <c r="J10" t="n">
+        <v>635</v>
+      </c>
+      <c r="K10" t="n">
         <v>634</v>
       </c>
-      <c r="K10" t="n">
-        <v>633</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.02990236218938669</v>
+        <v>0.02941150244473467</v>
       </c>
       <c r="M10" t="n">
-        <v>5.320218129980571</v>
+        <v>5.318823490321254</v>
       </c>
       <c r="N10" t="n">
-        <v>46.84462380023845</v>
+        <v>46.81023109754076</v>
       </c>
       <c r="O10" t="n">
-        <v>6.844313245332833</v>
+        <v>6.841800281909781</v>
       </c>
       <c r="P10" t="n">
-        <v>425.1125437653728</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>425.1294451391469</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>LINESTRING (174.71597829603397 -36.52450671650768, 174.7261335280038 -36.52315520555492)</t>
@@ -32537,7 +32550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K635"/>
+  <dimension ref="A1:K636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68719,6 +68732,63 @@
         </is>
       </c>
     </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>-36.51855466600359,174.72189419335763</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-36.51918881089096,174.7214157989307</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>-36.51982540594377,174.72097376140565</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>-36.520490420521035,174.72064321774877</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>-36.52118263244758,174.72046443340898</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>-36.521861878854374,174.7202485656138</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>-36.52256064238492,174.7200740980853</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>-36.523259841631585,174.72005212849422</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>-36.52388450067781,174.7206544631511</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0130/nzd0130.xlsx
+++ b/data/nzd0130/nzd0130.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K636"/>
+  <dimension ref="A1:K638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25240,6 +25240,84 @@
         <v>424.42</v>
       </c>
       <c r="K636" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>429.74</v>
+      </c>
+      <c r="C637" t="n">
+        <v>411.58</v>
+      </c>
+      <c r="D637" t="n">
+        <v>395.68</v>
+      </c>
+      <c r="E637" t="n">
+        <v>389.27</v>
+      </c>
+      <c r="F637" t="n">
+        <v>393.23</v>
+      </c>
+      <c r="G637" t="n">
+        <v>388.2</v>
+      </c>
+      <c r="H637" t="n">
+        <v>380.35</v>
+      </c>
+      <c r="I637" t="n">
+        <v>381.78</v>
+      </c>
+      <c r="J637" t="n">
+        <v>421.77</v>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>436.31</v>
+      </c>
+      <c r="C638" t="n">
+        <v>413.41</v>
+      </c>
+      <c r="D638" t="n">
+        <v>396.28</v>
+      </c>
+      <c r="E638" t="n">
+        <v>392.18</v>
+      </c>
+      <c r="F638" t="n">
+        <v>394.23</v>
+      </c>
+      <c r="G638" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="H638" t="n">
+        <v>380.85</v>
+      </c>
+      <c r="I638" t="n">
+        <v>381.94</v>
+      </c>
+      <c r="J638" t="n">
+        <v>422.73</v>
+      </c>
+      <c r="K638" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25256,7 +25334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B644"/>
+  <dimension ref="A1:B646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31699,6 +31777,26 @@
       </c>
       <c r="B644" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -31867,28 +31965,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2506373032691282</v>
+        <v>-0.2497800905114089</v>
       </c>
       <c r="J2" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K2" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02956482476578948</v>
+        <v>0.02955961135017482</v>
       </c>
       <c r="M2" t="n">
-        <v>8.035299515484454</v>
+        <v>8.019921186920529</v>
       </c>
       <c r="N2" t="n">
-        <v>111.8124471816835</v>
+        <v>111.5004080842512</v>
       </c>
       <c r="O2" t="n">
-        <v>10.57414049375567</v>
+        <v>10.5593753643031</v>
       </c>
       <c r="P2" t="n">
-        <v>438.317565218799</v>
+        <v>438.3085109840185</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31945,28 +32043,28 @@
         <v>0.0261</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1750300583643584</v>
+        <v>-0.1753795617216483</v>
       </c>
       <c r="J3" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K3" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0606311192584752</v>
+        <v>0.06125348533210573</v>
       </c>
       <c r="M3" t="n">
-        <v>4.031979102768275</v>
+        <v>4.022218917720739</v>
       </c>
       <c r="N3" t="n">
-        <v>25.73791560141779</v>
+        <v>25.66056233574464</v>
       </c>
       <c r="O3" t="n">
-        <v>5.073254931640808</v>
+        <v>5.065625562133925</v>
       </c>
       <c r="P3" t="n">
-        <v>417.6829803938992</v>
+        <v>417.6866640439168</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32023,28 +32121,28 @@
         <v>0.0367</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1376864173684013</v>
+        <v>-0.139132394464571</v>
       </c>
       <c r="J4" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K4" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06351078984663916</v>
+        <v>0.06512581741241186</v>
       </c>
       <c r="M4" t="n">
-        <v>3.078848129135118</v>
+        <v>3.076283857635096</v>
       </c>
       <c r="N4" t="n">
-        <v>15.13797531581615</v>
+        <v>15.10685071336793</v>
       </c>
       <c r="O4" t="n">
-        <v>3.890755108692418</v>
+        <v>3.886753235461177</v>
       </c>
       <c r="P4" t="n">
-        <v>401.9032175337979</v>
+        <v>401.9184757085492</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32101,28 +32199,28 @@
         <v>0.0459</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05451208644646736</v>
+        <v>-0.05509575191073133</v>
       </c>
       <c r="J5" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K5" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006153195389456356</v>
+        <v>0.006326632841399449</v>
       </c>
       <c r="M5" t="n">
-        <v>4.00210552772494</v>
+        <v>3.994672814257275</v>
       </c>
       <c r="N5" t="n">
-        <v>25.99169959828325</v>
+        <v>25.91938464858542</v>
       </c>
       <c r="O5" t="n">
-        <v>5.098205527269694</v>
+        <v>5.091108390968063</v>
       </c>
       <c r="P5" t="n">
-        <v>393.0869982177236</v>
+        <v>393.0931524522894</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32179,28 +32277,28 @@
         <v>0.0475</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01130913143874299</v>
+        <v>-0.01234136058039973</v>
       </c>
       <c r="J6" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K6" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002983515032369821</v>
+        <v>0.0003576466360427633</v>
       </c>
       <c r="M6" t="n">
-        <v>3.825022380166969</v>
+        <v>3.818044922763309</v>
       </c>
       <c r="N6" t="n">
-        <v>23.20764168000905</v>
+        <v>23.14376580815463</v>
       </c>
       <c r="O6" t="n">
-        <v>4.817431024935288</v>
+        <v>4.810796795558364</v>
       </c>
       <c r="P6" t="n">
-        <v>395.6564631334909</v>
+        <v>395.6673543884667</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32257,28 +32355,28 @@
         <v>0.0573</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02461946033906559</v>
+        <v>0.02138211142217709</v>
       </c>
       <c r="J7" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K7" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001372207580981999</v>
+        <v>0.001039138336559109</v>
       </c>
       <c r="M7" t="n">
-        <v>3.872516768384673</v>
+        <v>3.872924129448271</v>
       </c>
       <c r="N7" t="n">
-        <v>23.8875286753402</v>
+        <v>23.89426753957735</v>
       </c>
       <c r="O7" t="n">
-        <v>4.887486948866482</v>
+        <v>4.88817629996887</v>
       </c>
       <c r="P7" t="n">
-        <v>393.1999049505285</v>
+        <v>393.2340664011919</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32335,28 +32433,28 @@
         <v>0.0639</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08977982815941841</v>
+        <v>-0.0934261708292195</v>
       </c>
       <c r="J8" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K8" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01659980554171081</v>
+        <v>0.0180047011310982</v>
       </c>
       <c r="M8" t="n">
-        <v>3.986868384495617</v>
+        <v>3.986058443574228</v>
       </c>
       <c r="N8" t="n">
-        <v>25.89665963456459</v>
+        <v>25.91809143303879</v>
       </c>
       <c r="O8" t="n">
-        <v>5.088876067911714</v>
+        <v>5.090981382114729</v>
       </c>
       <c r="P8" t="n">
-        <v>388.7200664076109</v>
+        <v>388.7585257531354</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32413,28 +32511,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1609392567950386</v>
+        <v>-0.1649273003410749</v>
       </c>
       <c r="J9" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K9" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04448823923833745</v>
+        <v>0.04674784797624121</v>
       </c>
       <c r="M9" t="n">
-        <v>4.376453596771886</v>
+        <v>4.377833157702857</v>
       </c>
       <c r="N9" t="n">
-        <v>30.12625387435684</v>
+        <v>30.15426250311599</v>
       </c>
       <c r="O9" t="n">
-        <v>5.488738823660389</v>
+        <v>5.491289693971352</v>
       </c>
       <c r="P9" t="n">
-        <v>392.4013427510421</v>
+        <v>392.4434278502054</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32491,28 +32589,28 @@
         <v>0.0202</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1617363622499969</v>
+        <v>0.1571874489530097</v>
       </c>
       <c r="J10" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K10" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02941150244473467</v>
+        <v>0.02792304861724926</v>
       </c>
       <c r="M10" t="n">
-        <v>5.318823490321254</v>
+        <v>5.322132896786333</v>
       </c>
       <c r="N10" t="n">
-        <v>46.81023109754076</v>
+        <v>46.82353744854609</v>
       </c>
       <c r="O10" t="n">
-        <v>6.841800281909781</v>
+        <v>6.842772643347585</v>
       </c>
       <c r="P10" t="n">
-        <v>425.1294451391469</v>
+        <v>425.177429524988</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32550,7 +32648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K636"/>
+  <dimension ref="A1:K638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68789,6 +68887,120 @@
         </is>
       </c>
     </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>-36.51855466600359,174.72189419335763</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>-36.5191884780828,174.7214145240565</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>-36.51982231585434,174.72096103749317</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>-36.52049048992768,174.7206435415026</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>-36.521181853623,174.720459844002</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>-36.521861878854374,174.7202485656138</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>-36.52256107181477,174.72008335080196</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>-36.523259785879254,174.7200532429923</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>-36.52388838624153,174.7206252662832</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>-36.518572887017115,174.7219639922393</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>-36.519193553405685,174.72143396588922</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>-36.519823873882785,174.72096745291108</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-36.5204972223684,174.72067494562666</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>-36.521183707966955,174.7204707711616</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>-36.52186308161526,174.72026075766493</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>-36.522561330507116,174.72008892472772</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>-36.523259696675495,174.72005502618924</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>-36.523886978641904,174.72063584326216</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0130/nzd0130.xlsx
+++ b/data/nzd0130/nzd0130.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K638"/>
+  <dimension ref="A1:K641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25315,9 +25315,126 @@
         <v>381.94</v>
       </c>
       <c r="J638" t="n">
-        <v>422.73</v>
+        <v>425.09</v>
       </c>
       <c r="K638" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>436.25</v>
+      </c>
+      <c r="C639" t="n">
+        <v>414.52</v>
+      </c>
+      <c r="D639" t="n">
+        <v>396.48</v>
+      </c>
+      <c r="E639" t="n">
+        <v>391.89</v>
+      </c>
+      <c r="F639" t="n">
+        <v>394.46</v>
+      </c>
+      <c r="G639" t="n">
+        <v>390.62</v>
+      </c>
+      <c r="H639" t="n">
+        <v>382.13</v>
+      </c>
+      <c r="I639" t="n">
+        <v>382.52</v>
+      </c>
+      <c r="J639" t="n">
+        <v>425.22</v>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>436.25</v>
+      </c>
+      <c r="C640" t="n">
+        <v>414.52</v>
+      </c>
+      <c r="D640" t="n">
+        <v>396.37</v>
+      </c>
+      <c r="E640" t="n">
+        <v>392.31</v>
+      </c>
+      <c r="F640" t="n">
+        <v>394.49</v>
+      </c>
+      <c r="G640" t="n">
+        <v>391.05</v>
+      </c>
+      <c r="H640" t="n">
+        <v>382.22</v>
+      </c>
+      <c r="I640" t="n">
+        <v>382.31</v>
+      </c>
+      <c r="J640" t="n">
+        <v>427.35</v>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>437.08</v>
+      </c>
+      <c r="C641" t="n">
+        <v>414.74</v>
+      </c>
+      <c r="D641" t="n">
+        <v>396.73</v>
+      </c>
+      <c r="E641" t="n">
+        <v>392.4</v>
+      </c>
+      <c r="F641" t="n">
+        <v>394.48</v>
+      </c>
+      <c r="G641" t="n">
+        <v>391.49</v>
+      </c>
+      <c r="H641" t="n">
+        <v>382.11</v>
+      </c>
+      <c r="I641" t="n">
+        <v>381.92</v>
+      </c>
+      <c r="J641" t="n">
+        <v>429.08</v>
+      </c>
+      <c r="K641" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25334,7 +25451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B646"/>
+  <dimension ref="A1:B649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31797,6 +31914,36 @@
       </c>
       <c r="B646" t="n">
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>-0.62</v>
       </c>
     </row>
   </sheetData>
@@ -31965,28 +32112,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2497800905114089</v>
+        <v>-0.2451874026564727</v>
       </c>
       <c r="J2" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="K2" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02955961135017482</v>
+        <v>0.0287789536903621</v>
       </c>
       <c r="M2" t="n">
-        <v>8.019921186920529</v>
+        <v>8.002702263141087</v>
       </c>
       <c r="N2" t="n">
-        <v>111.5004080842512</v>
+        <v>111.0866871293343</v>
       </c>
       <c r="O2" t="n">
-        <v>10.5593753643031</v>
+        <v>10.53976693904255</v>
       </c>
       <c r="P2" t="n">
-        <v>438.3085109840185</v>
+        <v>438.2598756835562</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32043,28 +32190,28 @@
         <v>0.0261</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1753795617216483</v>
+        <v>-0.1738926632469218</v>
       </c>
       <c r="J3" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="K3" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06125348533210573</v>
+        <v>0.06085551845606041</v>
       </c>
       <c r="M3" t="n">
-        <v>4.022218917720739</v>
+        <v>4.010441134331984</v>
       </c>
       <c r="N3" t="n">
-        <v>25.66056233574464</v>
+        <v>25.55156978707804</v>
       </c>
       <c r="O3" t="n">
-        <v>5.065625562133925</v>
+        <v>5.054856059976193</v>
       </c>
       <c r="P3" t="n">
-        <v>417.6866640439168</v>
+        <v>417.6709182576216</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32121,28 +32268,28 @@
         <v>0.0367</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.139132394464571</v>
+        <v>-0.1407309472082216</v>
       </c>
       <c r="J4" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="K4" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06512581741241186</v>
+        <v>0.06713314773949486</v>
       </c>
       <c r="M4" t="n">
-        <v>3.076283857635096</v>
+        <v>3.069726976062559</v>
       </c>
       <c r="N4" t="n">
-        <v>15.10685071336793</v>
+        <v>15.04932971330858</v>
       </c>
       <c r="O4" t="n">
-        <v>3.886753235461177</v>
+        <v>3.879346557515657</v>
       </c>
       <c r="P4" t="n">
-        <v>401.9184757085492</v>
+        <v>401.9354095653497</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32199,28 +32346,28 @@
         <v>0.0459</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05509575191073133</v>
+        <v>-0.05455435171903141</v>
       </c>
       <c r="J5" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="K5" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006326632841399449</v>
+        <v>0.006268587387699753</v>
       </c>
       <c r="M5" t="n">
-        <v>3.994672814257275</v>
+        <v>3.978074148847968</v>
       </c>
       <c r="N5" t="n">
-        <v>25.91938464858542</v>
+        <v>25.79962643084727</v>
       </c>
       <c r="O5" t="n">
-        <v>5.091108390968063</v>
+        <v>5.079333266369442</v>
       </c>
       <c r="P5" t="n">
-        <v>393.0931524522894</v>
+        <v>393.087416161728</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32277,28 +32424,28 @@
         <v>0.0475</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01234136058039973</v>
+        <v>-0.01315608960476838</v>
       </c>
       <c r="J6" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="K6" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0003576466360427633</v>
+        <v>0.0004106506184303749</v>
       </c>
       <c r="M6" t="n">
-        <v>3.818044922763309</v>
+        <v>3.804069738504326</v>
       </c>
       <c r="N6" t="n">
-        <v>23.14376580815463</v>
+        <v>23.03870529702008</v>
       </c>
       <c r="O6" t="n">
-        <v>4.810796795558364</v>
+        <v>4.799865133211566</v>
       </c>
       <c r="P6" t="n">
-        <v>395.6673543884667</v>
+        <v>395.6759850713041</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32355,28 +32502,28 @@
         <v>0.0573</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02138211142217709</v>
+        <v>0.01878260619644262</v>
       </c>
       <c r="J7" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="K7" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001039138336559109</v>
+        <v>0.0008093098519708075</v>
       </c>
       <c r="M7" t="n">
-        <v>3.872924129448271</v>
+        <v>3.864803590809696</v>
       </c>
       <c r="N7" t="n">
-        <v>23.89426753957735</v>
+        <v>23.81773959785942</v>
       </c>
       <c r="O7" t="n">
-        <v>4.88817629996887</v>
+        <v>4.8803421599166</v>
       </c>
       <c r="P7" t="n">
-        <v>393.2340664011919</v>
+        <v>393.261602433102</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32433,28 +32580,28 @@
         <v>0.0639</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0934261708292195</v>
+        <v>-0.0973240005034246</v>
       </c>
       <c r="J8" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="K8" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0180047011310982</v>
+        <v>0.01965237765264816</v>
       </c>
       <c r="M8" t="n">
-        <v>3.986058443574228</v>
+        <v>3.980159348685461</v>
       </c>
       <c r="N8" t="n">
-        <v>25.91809143303879</v>
+        <v>25.87496572514958</v>
       </c>
       <c r="O8" t="n">
-        <v>5.090981382114729</v>
+        <v>5.08674411830884</v>
       </c>
       <c r="P8" t="n">
-        <v>388.7585257531354</v>
+        <v>388.799796670264</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32511,28 +32658,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1649273003410749</v>
+        <v>-0.1704222967119997</v>
       </c>
       <c r="J9" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="K9" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04674784797624121</v>
+        <v>0.0500110285208093</v>
       </c>
       <c r="M9" t="n">
-        <v>4.377833157702857</v>
+        <v>4.378167041263252</v>
       </c>
       <c r="N9" t="n">
-        <v>30.15426250311599</v>
+        <v>30.16899825922661</v>
       </c>
       <c r="O9" t="n">
-        <v>5.491289693971352</v>
+        <v>5.492631269184798</v>
       </c>
       <c r="P9" t="n">
-        <v>392.4434278502054</v>
+        <v>392.5016394336957</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32589,28 +32736,28 @@
         <v>0.0202</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1571874489530097</v>
+        <v>0.1559060940128891</v>
       </c>
       <c r="J10" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="K10" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02792304861724926</v>
+        <v>0.02776930268972166</v>
       </c>
       <c r="M10" t="n">
-        <v>5.322132896786333</v>
+        <v>5.302751829301078</v>
       </c>
       <c r="N10" t="n">
-        <v>46.82353744854609</v>
+        <v>46.59648551251544</v>
       </c>
       <c r="O10" t="n">
-        <v>6.842772643347585</v>
+        <v>6.826161843416506</v>
       </c>
       <c r="P10" t="n">
-        <v>425.177429524988</v>
+        <v>425.1910178807907</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32648,7 +32795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K638"/>
+  <dimension ref="A1:K641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68992,10 +69139,181 @@
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>-36.523886978641904,174.72063584326216</t>
+          <t>-36.523883518288876,174.72066184500022</t>
         </is>
       </c>
       <c r="K638" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>-36.518572720615346,174.72196335480643</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>-36.51919663187862,174.72144575847747</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>-36.519824393225534,174.7209695913838</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>-36.52049655143826,174.72067181600582</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>-36.52118413446592,174.72047328440834</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>-36.52186452492665,174.72027538812674</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>-36.52256199275833,174.72010319397776</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>-36.52325937331168,174.7200614902781</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>-36.523883327676046,174.72066327729928</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>-36.518572720615346,174.72196335480643</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>-36.51919663187862,174.72144575847747</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>-36.519824107587034,174.7209684152238</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-36.520497523130146,174.72067634856018</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>-36.52118419009622,174.72047361222315</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>-36.52186499509589,174.72028015411064</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>-36.52256203932279,174.7201041972844</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>-36.52325949039173,174.72005914983214</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>-36.52388020455571,174.72068674496737</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>-36.51857502250608,174.72197217262777</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>-36.51919724202629,174.72144809574732</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>-36.51982504240391,174.7209722644747</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>-36.52049773134982,174.72067731982182</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>-36.52118417155278,174.72047350295156</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>-36.52186547619908,174.7202850309314</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>-36.52256198241066,174.7201029710207</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>-36.52325970782597,174.72005480328963</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>-36.52387766793348,174.7207058055601</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0130/nzd0130.xlsx
+++ b/data/nzd0130/nzd0130.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K641"/>
+  <dimension ref="A1:K645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25435,6 +25435,162 @@
         <v>429.08</v>
       </c>
       <c r="K641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>438.95</v>
+      </c>
+      <c r="C642" t="n">
+        <v>415.79</v>
+      </c>
+      <c r="D642" t="n">
+        <v>397.34</v>
+      </c>
+      <c r="E642" t="n">
+        <v>393.52</v>
+      </c>
+      <c r="F642" t="n">
+        <v>396.51</v>
+      </c>
+      <c r="G642" t="n">
+        <v>393.52</v>
+      </c>
+      <c r="H642" t="n">
+        <v>385.2</v>
+      </c>
+      <c r="I642" t="n">
+        <v>383.78</v>
+      </c>
+      <c r="J642" t="n">
+        <v>428.11</v>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>436.5</v>
+      </c>
+      <c r="C643" t="n">
+        <v>414.43</v>
+      </c>
+      <c r="D643" t="n">
+        <v>396.81</v>
+      </c>
+      <c r="E643" t="n">
+        <v>393.09</v>
+      </c>
+      <c r="F643" t="n">
+        <v>396.44</v>
+      </c>
+      <c r="G643" t="n">
+        <v>393.08</v>
+      </c>
+      <c r="H643" t="n">
+        <v>384.92</v>
+      </c>
+      <c r="I643" t="n">
+        <v>383.34</v>
+      </c>
+      <c r="J643" t="n">
+        <v>428.27</v>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>438.66</v>
+      </c>
+      <c r="C644" t="n">
+        <v>414.81</v>
+      </c>
+      <c r="D644" t="n">
+        <v>396.7</v>
+      </c>
+      <c r="E644" t="n">
+        <v>393.69</v>
+      </c>
+      <c r="F644" t="n">
+        <v>397.66</v>
+      </c>
+      <c r="G644" t="n">
+        <v>393.4</v>
+      </c>
+      <c r="H644" t="n">
+        <v>385.62</v>
+      </c>
+      <c r="I644" t="n">
+        <v>383.16</v>
+      </c>
+      <c r="J644" t="n">
+        <v>432.44</v>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>436.33</v>
+      </c>
+      <c r="C645" t="n">
+        <v>414.45</v>
+      </c>
+      <c r="D645" t="n">
+        <v>396.35</v>
+      </c>
+      <c r="E645" t="n">
+        <v>393.33</v>
+      </c>
+      <c r="F645" t="n">
+        <v>397.82</v>
+      </c>
+      <c r="G645" t="n">
+        <v>393.26</v>
+      </c>
+      <c r="H645" t="n">
+        <v>385.88</v>
+      </c>
+      <c r="I645" t="n">
+        <v>382.76</v>
+      </c>
+      <c r="J645" t="n">
+        <v>430.87</v>
+      </c>
+      <c r="K645" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25451,7 +25607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B649"/>
+  <dimension ref="A1:B653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31944,6 +32100,46 @@
       </c>
       <c r="B649" t="n">
         <v>-0.62</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -32112,28 +32308,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2451874026564727</v>
+        <v>-0.2378282334592365</v>
       </c>
       <c r="J2" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="K2" t="n">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0287789536903621</v>
+        <v>0.02744204279446749</v>
       </c>
       <c r="M2" t="n">
-        <v>8.002702263141087</v>
+        <v>7.985333055038017</v>
       </c>
       <c r="N2" t="n">
-        <v>111.0866871293343</v>
+        <v>110.6165256475383</v>
       </c>
       <c r="O2" t="n">
-        <v>10.53976693904255</v>
+        <v>10.5174391202202</v>
       </c>
       <c r="P2" t="n">
-        <v>438.2598756835562</v>
+        <v>438.181587404214</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32190,28 +32386,28 @@
         <v>0.0261</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1738926632469218</v>
+        <v>-0.1715954078544364</v>
       </c>
       <c r="J3" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="K3" t="n">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06085551845606041</v>
+        <v>0.06008959517610524</v>
       </c>
       <c r="M3" t="n">
-        <v>4.010441134331984</v>
+        <v>3.99640220255678</v>
       </c>
       <c r="N3" t="n">
-        <v>25.55156978707804</v>
+        <v>25.4151478805201</v>
       </c>
       <c r="O3" t="n">
-        <v>5.054856059976193</v>
+        <v>5.04134385660412</v>
       </c>
       <c r="P3" t="n">
-        <v>417.6709182576216</v>
+        <v>417.6464835983295</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32268,28 +32464,28 @@
         <v>0.0367</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1407309472082216</v>
+        <v>-0.1424516717462174</v>
       </c>
       <c r="J4" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="K4" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06713314773949486</v>
+        <v>0.06951970740479085</v>
       </c>
       <c r="M4" t="n">
-        <v>3.069726976062559</v>
+        <v>3.05912995449612</v>
       </c>
       <c r="N4" t="n">
-        <v>15.04932971330858</v>
+        <v>14.96817863338848</v>
       </c>
       <c r="O4" t="n">
-        <v>3.879346557515657</v>
+        <v>3.868873044361689</v>
       </c>
       <c r="P4" t="n">
-        <v>401.9354095653497</v>
+        <v>401.9537280252199</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32346,28 +32542,28 @@
         <v>0.0459</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05455435171903141</v>
+        <v>-0.05233961275164286</v>
       </c>
       <c r="J5" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="K5" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006268587387699753</v>
+        <v>0.005849392430703149</v>
       </c>
       <c r="M5" t="n">
-        <v>3.978074148847968</v>
+        <v>3.961916471142856</v>
       </c>
       <c r="N5" t="n">
-        <v>25.79962643084727</v>
+        <v>25.65884166642167</v>
       </c>
       <c r="O5" t="n">
-        <v>5.079333266369442</v>
+        <v>5.06545572149453</v>
       </c>
       <c r="P5" t="n">
-        <v>393.087416161728</v>
+        <v>393.0638442873052</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32424,28 +32620,28 @@
         <v>0.0475</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01315608960476838</v>
+        <v>-0.01092525480212892</v>
       </c>
       <c r="J6" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="K6" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004106506184303749</v>
+        <v>0.0002869495926473009</v>
       </c>
       <c r="M6" t="n">
-        <v>3.804069738504326</v>
+        <v>3.791641365973103</v>
       </c>
       <c r="N6" t="n">
-        <v>23.03870529702008</v>
+        <v>22.91751430814674</v>
       </c>
       <c r="O6" t="n">
-        <v>4.799865133211566</v>
+        <v>4.787224071228204</v>
       </c>
       <c r="P6" t="n">
-        <v>395.6759850713041</v>
+        <v>395.6522329054037</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32502,28 +32698,28 @@
         <v>0.0573</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01878260619644262</v>
+        <v>0.01822471594147521</v>
       </c>
       <c r="J7" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="K7" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008093098519708075</v>
+        <v>0.0007726815092143902</v>
       </c>
       <c r="M7" t="n">
-        <v>3.864803590809696</v>
+        <v>3.842913147592347</v>
       </c>
       <c r="N7" t="n">
-        <v>23.81773959785942</v>
+        <v>23.67118113111617</v>
       </c>
       <c r="O7" t="n">
-        <v>4.8803421599166</v>
+        <v>4.865303806661632</v>
       </c>
       <c r="P7" t="n">
-        <v>393.261602433102</v>
+        <v>393.2675404292809</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32580,28 +32776,28 @@
         <v>0.0639</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0973240005034246</v>
+        <v>-0.09831663791878631</v>
       </c>
       <c r="J8" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="K8" t="n">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01965237765264816</v>
+        <v>0.02032055688629175</v>
       </c>
       <c r="M8" t="n">
-        <v>3.980159348685461</v>
+        <v>3.958643655677109</v>
       </c>
       <c r="N8" t="n">
-        <v>25.87496572514958</v>
+        <v>25.71872709598875</v>
       </c>
       <c r="O8" t="n">
-        <v>5.08674411830884</v>
+        <v>5.071363435604744</v>
       </c>
       <c r="P8" t="n">
-        <v>388.799796670264</v>
+        <v>388.8103509647419</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32658,28 +32854,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1704222967119997</v>
+        <v>-0.1762866291517588</v>
       </c>
       <c r="J9" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="K9" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0500110285208093</v>
+        <v>0.05380781847805938</v>
       </c>
       <c r="M9" t="n">
-        <v>4.378167041263252</v>
+        <v>4.373555908142342</v>
       </c>
       <c r="N9" t="n">
-        <v>30.16899825922661</v>
+        <v>30.11669636967499</v>
       </c>
       <c r="O9" t="n">
-        <v>5.492631269184798</v>
+        <v>5.487868107897181</v>
       </c>
       <c r="P9" t="n">
-        <v>392.5016394336957</v>
+        <v>392.5640576707212</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32736,28 +32932,28 @@
         <v>0.0202</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1559060940128891</v>
+        <v>0.1566230511444708</v>
       </c>
       <c r="J10" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="K10" t="n">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02776930268972166</v>
+        <v>0.02838861555570171</v>
       </c>
       <c r="M10" t="n">
-        <v>5.302751829301078</v>
+        <v>5.280926018465386</v>
       </c>
       <c r="N10" t="n">
-        <v>46.59648551251544</v>
+        <v>46.32910184149305</v>
       </c>
       <c r="O10" t="n">
-        <v>6.826161843416506</v>
+        <v>6.806548452886606</v>
       </c>
       <c r="P10" t="n">
-        <v>425.1910178807907</v>
+        <v>425.1833629800109</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32795,7 +32991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K641"/>
+  <dimension ref="A1:K645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69319,6 +69515,234 @@
         </is>
       </c>
     </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>-36.518580208691134,174.7219920392873</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>-36.51920015409398,174.72145925089936</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>-36.51982662639888,174.72097878681672</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>-36.52050032252726,174.72068940663397</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>-36.52118793586738,174.72049568508723</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>-36.5218676958317,174.72030753080966</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>-36.52256358111945,174.7201374178828</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>-36.52325867083047,174.72007553295373</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>-36.52387909020181,174.72069511840712</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>-36.518573413956,174.72196601077667</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>-36.51919638227276,174.72144480232163</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>-36.51982525014098,174.7209731198638</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>-36.520499327700364,174.72068476616136</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>-36.521187806063494,174.72049492018596</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>-36.52186721472943,174.72030265398865</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>-36.522563436253044,174.72013429648425</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>-36.52325891614155,174.72007062916228</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>-36.52387885560091,174.72069688123648</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>-36.51857940441666,174.72198895836132</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>-36.51919743616416,174.7214488394241</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>-36.519824964502504,174.7209719437038</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>-36.52050071583086,174.72069124123945</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>-36.521190068359004,174.72050825132263</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>-36.52186756462202,174.72030620076757</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>-36.5225637984189,174.72014209998065</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>-36.52325901649604,174.72006862306577</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>-36.52387274130596,174.72074282497329</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>-36.518572942484354,174.72196420471693</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>-36.519196437740725,174.7214450148007</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>-36.519824055652755,174.72096820137654</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>-36.52049988295259,174.72068735619257</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>-36.52119036505339,174.72050999966845</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>-36.52186741154404,174.72030464905177</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>-36.522563932937516,174.72014499842217</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>-36.52325923950586,174.72006416507347</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>-36.523875043332744,174.7207255272124</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0130/nzd0130.xlsx
+++ b/data/nzd0130/nzd0130.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K645"/>
+  <dimension ref="A1:K648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25593,6 +25593,123 @@
       <c r="K645" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>434.53</v>
+      </c>
+      <c r="C646" t="n">
+        <v>412.04</v>
+      </c>
+      <c r="D646" t="n">
+        <v>394.34</v>
+      </c>
+      <c r="E646" t="n">
+        <v>390.5</v>
+      </c>
+      <c r="F646" t="n">
+        <v>395.22</v>
+      </c>
+      <c r="G646" t="n">
+        <v>391.02</v>
+      </c>
+      <c r="H646" t="n">
+        <v>384.03</v>
+      </c>
+      <c r="I646" t="n">
+        <v>380.66</v>
+      </c>
+      <c r="J646" t="n">
+        <v>427.43</v>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>432.27</v>
+      </c>
+      <c r="C647" t="n">
+        <v>408.28</v>
+      </c>
+      <c r="D647" t="n">
+        <v>392.32</v>
+      </c>
+      <c r="E647" t="n">
+        <v>389.88</v>
+      </c>
+      <c r="F647" t="n">
+        <v>393.96</v>
+      </c>
+      <c r="G647" t="n">
+        <v>390.58</v>
+      </c>
+      <c r="H647" t="n">
+        <v>383.15</v>
+      </c>
+      <c r="I647" t="n">
+        <v>379.95</v>
+      </c>
+      <c r="J647" t="n">
+        <v>427.87</v>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>431.89</v>
+      </c>
+      <c r="C648" t="n">
+        <v>407.99</v>
+      </c>
+      <c r="D648" t="n">
+        <v>392.47</v>
+      </c>
+      <c r="E648" t="n">
+        <v>389.85</v>
+      </c>
+      <c r="F648" t="n">
+        <v>393.48</v>
+      </c>
+      <c r="G648" t="n">
+        <v>389.82</v>
+      </c>
+      <c r="H648" t="n">
+        <v>382.63</v>
+      </c>
+      <c r="I648" t="n">
+        <v>379.34</v>
+      </c>
+      <c r="J648" t="n">
+        <v>428.08</v>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25607,7 +25724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B653"/>
+  <dimension ref="A1:B656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32140,6 +32257,36 @@
       </c>
       <c r="B653" t="n">
         <v>0.49</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>-0.86</v>
       </c>
     </row>
   </sheetData>
@@ -32308,28 +32455,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2378282334592365</v>
+        <v>-0.2368187929556107</v>
       </c>
       <c r="J2" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K2" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02744204279446749</v>
+        <v>0.02749148752784658</v>
       </c>
       <c r="M2" t="n">
-        <v>7.985333055038017</v>
+        <v>7.95266160023993</v>
       </c>
       <c r="N2" t="n">
-        <v>110.6165256475383</v>
+        <v>110.1144598966158</v>
       </c>
       <c r="O2" t="n">
-        <v>10.5174391202202</v>
+        <v>10.49354372443436</v>
       </c>
       <c r="P2" t="n">
-        <v>438.181587404214</v>
+        <v>438.1708127238741</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32386,28 +32533,28 @@
         <v>0.0261</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1715954078544364</v>
+        <v>-0.1749612640550363</v>
       </c>
       <c r="J3" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K3" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06008959517610524</v>
+        <v>0.06276079806690182</v>
       </c>
       <c r="M3" t="n">
-        <v>3.99640220255678</v>
+        <v>3.995190558556029</v>
       </c>
       <c r="N3" t="n">
-        <v>25.4151478805201</v>
+        <v>25.37246477167887</v>
       </c>
       <c r="O3" t="n">
-        <v>5.04134385660412</v>
+        <v>5.037108771078789</v>
       </c>
       <c r="P3" t="n">
-        <v>417.6464835983295</v>
+        <v>417.6824756214239</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32464,28 +32611,28 @@
         <v>0.0367</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1424516717462174</v>
+        <v>-0.1471956543574283</v>
       </c>
       <c r="J4" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K4" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06951970740479085</v>
+        <v>0.07403635105878947</v>
       </c>
       <c r="M4" t="n">
-        <v>3.05912995449612</v>
+        <v>3.068073218406416</v>
       </c>
       <c r="N4" t="n">
-        <v>14.96817863338848</v>
+        <v>15.02111113552731</v>
       </c>
       <c r="O4" t="n">
-        <v>3.868873044361689</v>
+        <v>3.875707823808099</v>
       </c>
       <c r="P4" t="n">
-        <v>401.9537280252199</v>
+        <v>402.004454797775</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32542,28 +32689,28 @@
         <v>0.0459</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05233961275164286</v>
+        <v>-0.053818165315586</v>
       </c>
       <c r="J5" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K5" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005849392430703149</v>
+        <v>0.00624423664473206</v>
       </c>
       <c r="M5" t="n">
-        <v>3.961916471142856</v>
+        <v>3.952425341587674</v>
       </c>
       <c r="N5" t="n">
-        <v>25.65884166642167</v>
+        <v>25.55178438677006</v>
       </c>
       <c r="O5" t="n">
-        <v>5.06545572149453</v>
+        <v>5.054877287014004</v>
       </c>
       <c r="P5" t="n">
-        <v>393.0638442873052</v>
+        <v>393.0796545288619</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32620,28 +32767,28 @@
         <v>0.0475</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01092525480212892</v>
+        <v>-0.01198767133231006</v>
       </c>
       <c r="J6" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K6" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002869495926473009</v>
+        <v>0.0003489570202448444</v>
       </c>
       <c r="M6" t="n">
-        <v>3.791641365973103</v>
+        <v>3.779202139698025</v>
       </c>
       <c r="N6" t="n">
-        <v>22.91751430814674</v>
+        <v>22.81966627759364</v>
       </c>
       <c r="O6" t="n">
-        <v>4.787224071228204</v>
+        <v>4.776993434954003</v>
       </c>
       <c r="P6" t="n">
-        <v>395.6522329054037</v>
+        <v>395.6635995802811</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32698,28 +32845,28 @@
         <v>0.0573</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01822471594147521</v>
+        <v>0.01516858153223235</v>
       </c>
       <c r="J7" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K7" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007726815092143902</v>
+        <v>0.0005398718045638295</v>
       </c>
       <c r="M7" t="n">
-        <v>3.842913147592347</v>
+        <v>3.836514843689791</v>
       </c>
       <c r="N7" t="n">
-        <v>23.67118113111617</v>
+        <v>23.61173595340126</v>
       </c>
       <c r="O7" t="n">
-        <v>4.865303806661632</v>
+        <v>4.859190874353596</v>
       </c>
       <c r="P7" t="n">
-        <v>393.2675404292809</v>
+        <v>393.3002185320648</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32776,28 +32923,28 @@
         <v>0.0639</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09831663791878631</v>
+        <v>-0.1010220170366144</v>
       </c>
       <c r="J8" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K8" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02032055688629175</v>
+        <v>0.02161738971495186</v>
       </c>
       <c r="M8" t="n">
-        <v>3.958643655677109</v>
+        <v>3.948970352501532</v>
       </c>
       <c r="N8" t="n">
-        <v>25.71872709598875</v>
+        <v>25.63939486290061</v>
       </c>
       <c r="O8" t="n">
-        <v>5.071363435604744</v>
+        <v>5.063535806420313</v>
       </c>
       <c r="P8" t="n">
-        <v>388.8103509647419</v>
+        <v>388.8392668705166</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32854,28 +33001,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1762866291517588</v>
+        <v>-0.1836041330926678</v>
       </c>
       <c r="J9" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K9" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05380781847805938</v>
+        <v>0.05816096538387472</v>
       </c>
       <c r="M9" t="n">
-        <v>4.373555908142342</v>
+        <v>4.38241281970256</v>
       </c>
       <c r="N9" t="n">
-        <v>30.11669636967499</v>
+        <v>30.26029353770048</v>
       </c>
       <c r="O9" t="n">
-        <v>5.487868107897181</v>
+        <v>5.50093569656113</v>
       </c>
       <c r="P9" t="n">
-        <v>392.5640576707212</v>
+        <v>392.6422938401072</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32932,28 +33079,28 @@
         <v>0.0202</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1566230511444708</v>
+        <v>0.1551452250452421</v>
       </c>
       <c r="J10" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K10" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02838861555570171</v>
+        <v>0.02814814004444666</v>
       </c>
       <c r="M10" t="n">
-        <v>5.280926018465386</v>
+        <v>5.262818707069476</v>
       </c>
       <c r="N10" t="n">
-        <v>46.32910184149305</v>
+        <v>46.12581460786308</v>
       </c>
       <c r="O10" t="n">
-        <v>6.806548452886606</v>
+        <v>6.791598825597923</v>
       </c>
       <c r="P10" t="n">
-        <v>425.1833629800109</v>
+        <v>425.1991535232312</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32991,7 +33138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K645"/>
+  <dimension ref="A1:K648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69743,6 +69890,177 @@
         </is>
       </c>
     </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>-36.518567950430054,174.72194508173249</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>-36.51918975384733,174.72141941107435</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>-36.51981883625617,174.72094670972737</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>-36.520493335599525,174.7206568154101</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>-36.52118554376646,174.72048158905005</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>-36.52186496229339,174.72027982160012</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>-36.52256297578428,174.72012437489607</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>-36.52326041030475,174.72004076061353</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>-36.52388008725533,174.72068762638207</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>-36.51856168262408,174.7219210717665</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>-36.51917932585303,174.72137946502002</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>-36.51981359088843,174.7209251111573</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>-36.52049190119602,174.72065012449727</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>-36.52118320729418,174.72046782082845</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>-36.52186448118997,174.7202749447794</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>-36.52256252048851,174.72011456478648</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>-36.523260806145245,174.72003284767686</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>-36.52387944210311,174.720692474163</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>-36.51856062874472,174.72191703469295</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>-36.51917852156566,174.7213763840748</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>-36.51981398039609,174.72092671501144</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>-36.52049183178938,174.72064980074342</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>-36.52118231720909,174.72046257579183</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>-36.521863650192685,174.72026652118015</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>-36.52256225144973,174.72010876790358</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>-36.52326114623314,174.72002604923824</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>-36.52387913418947,174.7206947878766</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
